--- a/reference/SAMPLE.xlsx
+++ b/reference/SAMPLE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kcassidy\Documents\GitHub\quiz_processing_system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kcassidy\Documents\GitHub\quiz_processing_system\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8DC237-4E23-4BBD-9257-52E3D17C50C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D51D2B8-9815-40A7-86A9-755F583FB0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58413554-941A-47F6-8893-9DE0674C0595}"/>
   </bookViews>
@@ -207,10 +207,10 @@
     </r>
   </si>
   <si>
-    <t>blank</t>
-  </si>
-  <si>
-    <t>Want to practice before using your own roster and file? Try adding this class to the Quiz Processing System, and use the file called "Sample_Quiz.pdf"</t>
+    <t>reserved</t>
+  </si>
+  <si>
+    <t>Want to practice before using your own roster and file? Try adding this class to the Quiz Processing System, and use the file called "SAMPLE.pdf" found in the reference folder.</t>
   </si>
 </sst>
 </file>
@@ -638,7 +638,7 @@
         <v>49</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
